--- a/results/Int Task Remove ACC -0.7/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_1_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8207128641898456</v>
+        <v>0.8308765079275251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8200956396253642</v>
+        <v>0.834989389094819</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8039812116238929</v>
+        <v>0.8330573554794715</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8027820378597097</v>
+        <v>0.8298948341397621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7933923771257181</v>
+        <v>0.8292776095752808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.793792101713779</v>
+        <v>0.8296165926261283</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7898967205229054</v>
+        <v>0.8279726097167597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7867851315280647</v>
+        <v>0.8251236052554634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7867851315280647</v>
+        <v>0.8254625883063109</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.788975788272356</v>
+        <v>0.8205444101751507</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.788777906680626</v>
+        <v>0.8272084359054168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7876394744536563</v>
+        <v>0.8357084783490375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7876747498184355</v>
+        <v>0.8357084783490375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7796351735000896</v>
+        <v>0.8358299614234648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7888269526423511</v>
+        <v>0.8345093045848542</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7779540288427983</v>
+        <v>0.826444262094074</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7895245371287363</v>
+        <v>0.8283566773247314</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7824822915782425</v>
+        <v>0.8142663384359997</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7838734991464116</v>
+        <v>0.800949982550956</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.781263499429369</v>
+        <v>0.8169193476887091</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7757946860586853</v>
+        <v>0.8145366571404318</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7717483942163493</v>
+        <v>0.8179578016090848</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7712526527262953</v>
+        <v>0.8109449836356262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.770543372664422</v>
+        <v>0.8112232251492602</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7582184997594861</v>
+        <v>0.803269856540562</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7519855125774596</v>
+        <v>0.8008362336474162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7518836478877224</v>
+        <v>0.7945973986776455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7392550672967186</v>
+        <v>0.7747188817520727</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7584712751006857</v>
+        <v>0.7789885213585732</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7573935844109296</v>
+        <v>0.7721990511492789</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7583654490063476</v>
+        <v>0.7788670382841459</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7440947718891184</v>
+        <v>0.7788572290918008</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7314778868736029</v>
+        <v>0.7788572290918008</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7363098572951152</v>
+        <v>0.7729279495958424</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7363098572951152</v>
+        <v>0.7626486705714798</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7402974826216953</v>
+        <v>0.748750365486734</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7289052375427973</v>
+        <v>0.7522871452420701</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7289052375427973</v>
+        <v>0.7477843486790602</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7321011478641426</v>
+        <v>0.7520441790932156</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7377521858464673</v>
+        <v>0.7554849419465588</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7308470803504901</v>
+        <v>0.7531728021278402</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7333159786084151</v>
+        <v>0.7182750912537845</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.747224092885506</v>
+        <v>0.708125218113051</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7503964234175603</v>
+        <v>0.7077862350622035</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.744294728502306</v>
+        <v>0.7185337143827283</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7503866142252152</v>
+        <v>0.7170210237401318</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6734923554323118</v>
+        <v>0.7072003244579006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6794372919083596</v>
+        <v>0.7144287560246361</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6770996859172067</v>
+        <v>0.7045375060128463</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6563668260660422</v>
+        <v>0.7045375060128463</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6261933731360176</v>
+        <v>0.6715895607556851</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6215534365184913</v>
+        <v>0.6355181422898805</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6164784999481245</v>
+        <v>0.6145345821189743</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5622040500646086</v>
+        <v>0.6215062769399093</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5529692613866802</v>
+        <v>0.6494675683578092</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5494990709563019</v>
+        <v>0.6429367212774586</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5437461682842402</v>
+        <v>0.6310623166671383</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5406385406940003</v>
+        <v>0.6187236731652566</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5745309979910019</v>
+        <v>0.5272818162096904</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5727753411995511</v>
+        <v>0.4934501004499023</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5827450647501013</v>
+        <v>0.488941267460834</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6424702187261254</v>
+        <v>0.5144983635626232</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5969223659017383</v>
+        <v>0.5246127727002632</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6109617724456015</v>
+        <v>0.5125446365411279</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6098488063910661</v>
+        <v>0.5188598700282014</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6212959452194335</v>
+        <v>0.5128953151674637</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.575785820057912</v>
+        <v>0.5027924129669977</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5785093800401799</v>
+        <v>0.5027924129669977</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5685239995095404</v>
+        <v>0.5027924129669977</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5605666694962413</v>
+        <v>0.5087216924629562</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5559912471822152</v>
+        <v>0.4724329626590457</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5694311611631439</v>
+        <v>0.482404383954425</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5886494439885686</v>
+        <v>0.4905341293870198</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5862314780755119</v>
+        <v>0.4984307178631052</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.592241117493374</v>
+        <v>0.4923956122728088</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5737673900946021</v>
+        <v>0.4928208030333041</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5221319902285353</v>
+        <v>0.5098110787282005</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5107750205144167</v>
+        <v>0.4852965865897023</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5100617790479425</v>
+        <v>0.4945391094385181</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5100617790479425</v>
+        <v>0.4989851258689152</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5086352961149939</v>
+        <v>0.4992477104024599</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5113569697141186</v>
+        <v>0.4898012695358555</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5116352112277525</v>
+        <v>0.4751565226413137</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5116352112277525</v>
+        <v>0.4952446167341049</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5116352112277525</v>
+        <v>0.5085981343670712</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5116352112277525</v>
+        <v>0.5093721173707592</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5066642143685804</v>
+        <v>0.5163164596361167</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5016481329522839</v>
+        <v>0.4920900182035973</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4928285372041916</v>
+        <v>0.4929698273016233</v>
       </c>
     </row>
   </sheetData>
